--- a/Data/CRIME-Q_Appraisal_Template.xlsx
+++ b/Data/CRIME-Q_Appraisal_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/annalenz/Desktop/ChronicNoise_Rodents/Prenatal_Chronic_Noise/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BA0612C-B0F1-944E-8086-D429B035C8F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A98D07FE-24F3-2940-98E2-23302ABAD4AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,6 +35,7 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
           </rPr>
           <t>Domain/Type: ID
 Item code: 0
@@ -52,6 +53,7 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
           </rPr>
           <t>Domain/Type: ID
 Item code: 0
@@ -69,6 +71,7 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
           </rPr>
           <t>Domain/Type: QoR
 Item code: 1X
@@ -86,6 +89,7 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
           </rPr>
           <t>Domain/Type: QoR
 Item code: 1Xn
@@ -103,6 +107,7 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
           </rPr>
           <t>Domain/Type: QoR
 Item code: 3X
@@ -120,6 +125,7 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
           </rPr>
           <t>Domain/Type: QoR
 Item code: 3Xn
@@ -137,6 +143,7 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
           </rPr>
           <t>Domain/Type: MQ
 Item code: 3Y
@@ -154,6 +161,7 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
           </rPr>
           <t>Domain/Type: MQ
 Item code: 3Yn
@@ -171,6 +179,7 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
           </rPr>
           <t>Domain/Type: RoB
 Item code: 3Z
@@ -188,6 +197,7 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
           </rPr>
           <t>Domain/Type: RoB
 Item code: 3Zn
@@ -205,6 +215,7 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
           </rPr>
           <t>Domain/Type: QoR
 Item code: 4Y
@@ -222,6 +233,7 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
           </rPr>
           <t>Domain/Type: QoR
 Item code: 4Yn
@@ -239,6 +251,7 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
           </rPr>
           <t>Domain/Type: QoR
 Item code: 5X
@@ -256,6 +269,7 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
           </rPr>
           <t>Domain/Type: QoR
 Item code: 5Xn
@@ -273,6 +287,7 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
           </rPr>
           <t>Domain/Type: MQ
 Item code: 5Y
@@ -290,6 +305,7 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
           </rPr>
           <t>Domain/Type: MQ
 Item code: 5Yn
@@ -307,6 +323,7 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
           </rPr>
           <t>Domain/Type: RoB
 Item code: 5Z (1)
@@ -324,6 +341,7 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
           </rPr>
           <t>Domain/Type: RoB
 Item code: 5Z (1)n
@@ -341,6 +359,7 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
           </rPr>
           <t>Domain/Type: RoB
 Item code: 5Z (2)
@@ -358,6 +377,7 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
           </rPr>
           <t>Domain/Type: RoB
 Item code: 5Z (2)n
@@ -375,6 +395,7 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
           </rPr>
           <t>Domain/Type: RoB
 Item code: 5Z (3)
@@ -392,6 +413,7 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
           </rPr>
           <t>Domain/Type: RoB
 Item code: 5Z (3)n
@@ -409,6 +431,7 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
           </rPr>
           <t>Domain/Type: QoR
 Item code: 6X
@@ -426,6 +449,7 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
           </rPr>
           <t>Domain/Type: QoR
 Item code: 6Xn
@@ -443,6 +467,7 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
           </rPr>
           <t>Domain/Type: QoR
 Item code: 7X
@@ -460,6 +485,7 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
           </rPr>
           <t>Domain/Type: QoR
 Item code: 7Xn
@@ -477,6 +503,7 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
           </rPr>
           <t>Domain/Type: QoR
 Item code: 8X
@@ -494,6 +521,7 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
           </rPr>
           <t>Domain/Type: QoR
 Item code: 8Xn
@@ -511,6 +539,7 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
           </rPr>
           <t>Domain/Type: RoB
 Item code: 8Z (1)
@@ -528,6 +557,7 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
           </rPr>
           <t>Domain/Type: RoB
 Item code: 8Z (1)n
@@ -545,6 +575,7 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
           </rPr>
           <t>Domain/Type: RoB
 Item code: 8Z (2)
@@ -562,6 +593,7 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
           </rPr>
           <t>Domain/Type: RoB
 Item code: 8Z (2)n
@@ -579,6 +611,7 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
           </rPr>
           <t>Domain/Type: QoR
 Item code: 9X
@@ -596,6 +629,7 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
           </rPr>
           <t>Domain/Type: QoR
 Item code: 9Xn
@@ -613,6 +647,7 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
           </rPr>
           <t>Domain/Type: QoR
 Item code: 10X
@@ -630,6 +665,7 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
           </rPr>
           <t>Domain/Type: QoR
 Item code: 10Xn
@@ -647,6 +683,7 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
           </rPr>
           <t>Domain/Type: RoB
 Item code: 10Z
@@ -664,6 +701,7 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
           </rPr>
           <t>Domain/Type: RoB
 Item code: 10Zn
@@ -681,6 +719,7 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
           </rPr>
           <t>Domain/Type: QoR
 Item code: 11X
@@ -698,6 +737,7 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
           </rPr>
           <t>Domain/Type: QoR
 Item code: 11X_n
@@ -715,6 +755,7 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
           </rPr>
           <t>Domain/Type: QoR
 Item code: 12X
@@ -732,6 +773,7 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
           </rPr>
           <t>Domain/Type: QoR
 Item code: 12X_n
@@ -749,6 +791,7 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
           </rPr>
           <t>Domain/Type: QoR
 Item code: 13X
@@ -766,6 +809,7 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
           </rPr>
           <t>Domain/Type: QoR
 Item code: 13X_n
@@ -1261,9 +1305,6 @@
 contributions to statistical analyses"</t>
   </si>
   <si>
-    <t>morra_1965_physiolrec.pdf</t>
-  </si>
-  <si>
     <t>PRENATAL SOUND STIMULATION ON POSTNATAL RAT OFFSPRING OPEN FIELD BEHAVIORS</t>
   </si>
   <si>
@@ -3193,6 +3234,9 @@
       </rPr>
       <t>"NA"</t>
     </r>
+  </si>
+  <si>
+    <t>morra_1965_physiolrec</t>
   </si>
 </sst>
 </file>
@@ -3479,15 +3523,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -3527,13 +3562,22 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3597,6 +3641,60 @@
             <a:srgbClr val="000000"/>
           </a:solidFill>
           <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>584200</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>127000</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="AutoShape 46">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7615DAC0-D65C-4E75-A35E-04CAA9491A4B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="12700000" cy="12700000"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst/>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
           <a:headEnd/>
           <a:tailEnd/>
         </a:ln>
@@ -5443,10 +5541,10 @@
     </row>
     <row r="13" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A13" s="7" t="s">
+        <v>381</v>
+      </c>
+      <c r="B13" s="7" t="s">
         <v>149</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>150</v>
       </c>
       <c r="C13" s="16" t="s">
         <v>47</v>
@@ -5455,7 +5553,7 @@
         <v>48</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G13" s="7" t="s">
         <v>48</v>
@@ -5467,19 +5565,19 @@
         <v>51</v>
       </c>
       <c r="J13" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="K13" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="L13" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="M13" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="N13" s="7" t="s">
         <v>152</v>
-      </c>
-      <c r="K13" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="L13" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="M13" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="N13" s="7" t="s">
-        <v>153</v>
       </c>
       <c r="O13" s="7" t="s">
         <v>48</v>
@@ -5497,7 +5595,7 @@
         <v>51</v>
       </c>
       <c r="T13" s="7" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="U13" s="7" t="s">
         <v>51</v>
@@ -5527,7 +5625,7 @@
         <v>51</v>
       </c>
       <c r="AD13" s="7" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="AE13" s="7" t="s">
         <v>51</v>
@@ -5577,10 +5675,10 @@
     </row>
     <row r="14" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
+        <v>155</v>
+      </c>
+      <c r="B14" s="13" t="s">
         <v>156</v>
-      </c>
-      <c r="B14" s="13" t="s">
-        <v>157</v>
       </c>
       <c r="C14" s="7" t="s">
         <v>47</v>
@@ -5589,13 +5687,13 @@
         <v>48</v>
       </c>
       <c r="F14" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="H14" s="7" t="s">
         <v>158</v>
-      </c>
-      <c r="G14" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="H14" s="7" t="s">
-        <v>159</v>
       </c>
       <c r="I14" s="7" t="s">
         <v>51</v>
@@ -5613,7 +5711,7 @@
         <v>48</v>
       </c>
       <c r="N14" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="O14" s="7" t="s">
         <v>48</v>
@@ -5625,7 +5723,7 @@
         <v>51</v>
       </c>
       <c r="R14" s="7" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="S14" s="7" t="s">
         <v>51</v>
@@ -5643,25 +5741,25 @@
         <v>47</v>
       </c>
       <c r="X14" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="Y14" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="Z14" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="AA14" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="AB14" s="7" t="s">
         <v>162</v>
-      </c>
-      <c r="Y14" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="Z14" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="AA14" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="AB14" s="7" t="s">
-        <v>163</v>
       </c>
       <c r="AC14" s="7" t="s">
         <v>47</v>
       </c>
       <c r="AD14" s="7" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AE14" s="7" t="s">
         <v>51</v>
@@ -5679,7 +5777,7 @@
         <v>47</v>
       </c>
       <c r="AJ14" s="7" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AK14" s="7" t="s">
         <v>47</v>
@@ -5691,19 +5789,19 @@
         <v>47</v>
       </c>
       <c r="AN14" s="7" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AO14" s="7" t="s">
         <v>47</v>
       </c>
       <c r="AP14" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="AQ14" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR14" s="7" t="s">
         <v>167</v>
-      </c>
-      <c r="AQ14" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="AR14" s="7" t="s">
-        <v>168</v>
       </c>
       <c r="AS14" s="7">
         <v>20</v>
@@ -5711,10 +5809,10 @@
     </row>
     <row r="15" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A15" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="B15" s="7" t="s">
         <v>169</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>170</v>
       </c>
       <c r="C15" s="7" t="s">
         <v>47</v>
@@ -5723,7 +5821,7 @@
         <v>48</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G15" s="7" t="s">
         <v>48</v>
@@ -5735,19 +5833,19 @@
         <v>51</v>
       </c>
       <c r="J15" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="K15" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="L15" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="M15" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="N15" s="7" t="s">
         <v>172</v>
-      </c>
-      <c r="K15" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="L15" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="M15" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="N15" s="7" t="s">
-        <v>173</v>
       </c>
       <c r="O15" s="7" t="s">
         <v>48</v>
@@ -5777,25 +5875,25 @@
         <v>47</v>
       </c>
       <c r="X15" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="Y15" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="Z15" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="AA15" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="AB15" s="7" t="s">
         <v>174</v>
       </c>
-      <c r="Y15" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="Z15" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="AA15" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="AB15" s="7" t="s">
-        <v>175</v>
-      </c>
       <c r="AC15" s="7" t="s">
         <v>53</v>
       </c>
       <c r="AD15" s="7" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="AE15" s="7" t="s">
         <v>51</v>
@@ -5813,7 +5911,7 @@
         <v>47</v>
       </c>
       <c r="AJ15" s="7" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AK15" s="7" t="s">
         <v>53</v>
@@ -5831,7 +5929,7 @@
         <v>47</v>
       </c>
       <c r="AP15" s="7" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AQ15" s="7" t="s">
         <v>64</v>
@@ -5845,19 +5943,19 @@
     </row>
     <row r="16" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A16" s="17" t="s">
+        <v>177</v>
+      </c>
+      <c r="B16" s="7" t="s">
         <v>178</v>
       </c>
-      <c r="B16" s="7" t="s">
+      <c r="C16" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F16" s="7" t="s">
         <v>179</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="F16" s="7" t="s">
-        <v>180</v>
       </c>
       <c r="G16" s="7" t="s">
         <v>48</v>
@@ -5881,7 +5979,7 @@
         <v>48</v>
       </c>
       <c r="N16" s="7" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="O16" s="7" t="s">
         <v>48</v>
@@ -5893,7 +5991,7 @@
         <v>51</v>
       </c>
       <c r="R16" s="7" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="S16" s="7" t="s">
         <v>51</v>
@@ -5929,7 +6027,7 @@
         <v>51</v>
       </c>
       <c r="AD16" s="7" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AE16" s="7" t="s">
         <v>51</v>
@@ -5976,10 +6074,10 @@
     </row>
     <row r="17" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A17" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="B17" s="7" t="s">
         <v>184</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>185</v>
       </c>
       <c r="C17" s="7" t="s">
         <v>47</v>
@@ -6012,7 +6110,7 @@
         <v>48</v>
       </c>
       <c r="N17" s="7" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="O17" s="7" t="s">
         <v>48</v>
@@ -6024,13 +6122,13 @@
         <v>51</v>
       </c>
       <c r="R17" s="7" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="S17" s="7" t="s">
         <v>51</v>
       </c>
       <c r="T17" s="7" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="U17" s="7" t="s">
         <v>51</v>
@@ -6042,25 +6140,25 @@
         <v>47</v>
       </c>
       <c r="X17" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="Y17" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="Z17" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="AA17" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="AB17" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="Y17" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="Z17" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="AA17" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="AB17" s="7" t="s">
-        <v>189</v>
-      </c>
       <c r="AC17" s="7" t="s">
         <v>51</v>
       </c>
       <c r="AD17" s="7" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AE17" s="7" t="s">
         <v>51</v>
@@ -6072,7 +6170,7 @@
         <v>53</v>
       </c>
       <c r="AH17" s="7" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AI17" s="7" t="s">
         <v>53</v>
@@ -6084,7 +6182,7 @@
         <v>47</v>
       </c>
       <c r="AL17" s="7" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AM17" s="7" t="s">
         <v>53</v>
@@ -6096,7 +6194,7 @@
         <v>47</v>
       </c>
       <c r="AP17" s="7" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="AQ17" s="7" t="s">
         <v>53</v>
@@ -6182,76 +6280,76 @@
   <dimension ref="A1:E61"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="17.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.83203125" style="24" customWidth="1"/>
-    <col min="2" max="2" width="24.1640625" style="24" customWidth="1"/>
-    <col min="3" max="3" width="6.5" style="24" customWidth="1"/>
-    <col min="4" max="4" width="39" style="24" customWidth="1"/>
-    <col min="5" max="5" width="51.6640625" style="24" customWidth="1"/>
-    <col min="6" max="16384" width="17.83203125" style="24"/>
+    <col min="1" max="1" width="9.83203125" style="21" customWidth="1"/>
+    <col min="2" max="2" width="24.1640625" style="21" customWidth="1"/>
+    <col min="3" max="3" width="6.5" style="21" customWidth="1"/>
+    <col min="4" max="4" width="39" style="21" customWidth="1"/>
+    <col min="5" max="5" width="51.6640625" style="21" customWidth="1"/>
+    <col min="6" max="16384" width="17.83203125" style="21"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A1" s="6" t="s">
-        <v>193</v>
-      </c>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
+        <v>192</v>
+      </c>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="18" t="s">
+        <v>193</v>
+      </c>
+      <c r="B2" s="19" t="s">
         <v>194</v>
       </c>
-      <c r="B2" s="19" t="s">
+      <c r="C2" s="18" t="s">
         <v>195</v>
-      </c>
-      <c r="C2" s="18" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="16" t="s">
+        <v>196</v>
+      </c>
+      <c r="B3" s="23" t="s">
         <v>197</v>
       </c>
-      <c r="B3" s="26" t="s">
+      <c r="C3" s="16" t="s">
         <v>198</v>
-      </c>
-      <c r="C3" s="16" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="16" t="s">
+        <v>199</v>
+      </c>
+      <c r="B4" s="24" t="s">
         <v>200</v>
       </c>
-      <c r="B4" s="27" t="s">
+      <c r="C4" s="16" t="s">
         <v>201</v>
-      </c>
-      <c r="C4" s="16" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="16" t="s">
+        <v>202</v>
+      </c>
+      <c r="B5" s="25" t="s">
         <v>203</v>
       </c>
-      <c r="B5" s="28" t="s">
+      <c r="C5" s="16" t="s">
         <v>204</v>
       </c>
-      <c r="C5" s="16" t="s">
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A6" s="26" t="s">
         <v>205</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A6" s="29" t="s">
+      <c r="B6" s="27" t="s">
         <v>206</v>
       </c>
-      <c r="B6" s="30" t="s">
+      <c r="C6" s="26" t="s">
         <v>207</v>
       </c>
-      <c r="C6" s="29" t="s">
-        <v>208</v>
-      </c>
-      <c r="D6" s="31"/>
+      <c r="D6" s="28"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="16"/>
@@ -6259,849 +6357,849 @@
       <c r="C7" s="16"/>
     </row>
     <row r="8" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A8" s="32" t="s">
+      <c r="A8" s="29" t="s">
+        <v>208</v>
+      </c>
+      <c r="B8" s="29"/>
+      <c r="C8" s="29" t="s">
         <v>209</v>
       </c>
-      <c r="B8" s="32"/>
-      <c r="C8" s="32" t="s">
+      <c r="D8" s="29" t="s">
         <v>210</v>
       </c>
-      <c r="D8" s="32" t="s">
+      <c r="E8" s="29" t="s">
         <v>211</v>
       </c>
-      <c r="E8" s="32" t="s">
+    </row>
+    <row r="9" spans="1:5" ht="168" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="30">
+        <v>0</v>
+      </c>
+      <c r="B9" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="C9" s="30" t="s">
+        <v>196</v>
+      </c>
+      <c r="D9" s="30" t="s">
         <v>212</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" ht="168" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="33">
+      <c r="E9" s="30" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A10" s="30">
         <v>0</v>
       </c>
-      <c r="B9" s="33" t="s">
-        <v>0</v>
-      </c>
-      <c r="C9" s="33" t="s">
-        <v>197</v>
-      </c>
-      <c r="D9" s="33" t="s">
-        <v>213</v>
-      </c>
-      <c r="E9" s="33" t="s">
+      <c r="B10" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="C10" s="30" t="s">
+        <v>196</v>
+      </c>
+      <c r="D10" s="30" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A10" s="33">
-        <v>0</v>
-      </c>
-      <c r="B10" s="33" t="s">
-        <v>1</v>
-      </c>
-      <c r="C10" s="33" t="s">
-        <v>197</v>
-      </c>
-      <c r="D10" s="33" t="s">
+      <c r="E10" s="30" t="s">
         <v>215</v>
       </c>
-      <c r="E10" s="33" t="s">
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A11" s="35" t="s">
         <v>216</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A11" s="34" t="s">
+      <c r="B11" s="35"/>
+      <c r="C11" s="35"/>
+      <c r="D11" s="35"/>
+      <c r="E11" s="35"/>
+    </row>
+    <row r="12" spans="1:5" ht="48" x14ac:dyDescent="0.2">
+      <c r="A12" s="30" t="s">
         <v>217</v>
       </c>
-      <c r="B11" s="34"/>
-      <c r="C11" s="34"/>
-      <c r="D11" s="34"/>
-      <c r="E11" s="34"/>
-    </row>
-    <row r="12" spans="1:5" ht="48" x14ac:dyDescent="0.2">
-      <c r="A12" s="33" t="s">
+      <c r="B12" s="30" t="s">
         <v>218</v>
       </c>
-      <c r="B12" s="33" t="s">
+      <c r="C12" s="30" t="s">
+        <v>199</v>
+      </c>
+      <c r="D12" s="30" t="s">
+        <v>342</v>
+      </c>
+      <c r="E12" s="30" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A13" s="30" t="s">
         <v>219</v>
       </c>
-      <c r="C12" s="33" t="s">
-        <v>200</v>
-      </c>
-      <c r="D12" s="33" t="s">
-        <v>343</v>
-      </c>
-      <c r="E12" s="33" t="s">
+      <c r="B13" s="30" t="s">
+        <v>220</v>
+      </c>
+      <c r="C13" s="30" t="s">
+        <v>199</v>
+      </c>
+      <c r="D13" s="30" t="s">
+        <v>221</v>
+      </c>
+      <c r="E13" s="30" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="112" x14ac:dyDescent="0.2">
+      <c r="A14" s="30" t="s">
+        <v>223</v>
+      </c>
+      <c r="B14" s="30" t="s">
+        <v>224</v>
+      </c>
+      <c r="C14" s="30" t="s">
+        <v>199</v>
+      </c>
+      <c r="D14" s="30" t="s">
         <v>344</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A13" s="33" t="s">
-        <v>220</v>
-      </c>
-      <c r="B13" s="33" t="s">
-        <v>221</v>
-      </c>
-      <c r="C13" s="33" t="s">
-        <v>200</v>
-      </c>
-      <c r="D13" s="33" t="s">
+      <c r="E14" s="30" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A15" s="30" t="s">
+        <v>225</v>
+      </c>
+      <c r="B15" s="30" t="s">
+        <v>226</v>
+      </c>
+      <c r="C15" s="30" t="s">
+        <v>199</v>
+      </c>
+      <c r="D15" s="30" t="s">
+        <v>227</v>
+      </c>
+      <c r="E15" s="30" t="s">
         <v>222</v>
       </c>
-      <c r="E13" s="33" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="112" x14ac:dyDescent="0.2">
-      <c r="A14" s="33" t="s">
-        <v>224</v>
-      </c>
-      <c r="B14" s="33" t="s">
-        <v>225</v>
-      </c>
-      <c r="C14" s="33" t="s">
-        <v>200</v>
-      </c>
-      <c r="D14" s="33" t="s">
-        <v>345</v>
-      </c>
-      <c r="E14" s="33" t="s">
+    </row>
+    <row r="16" spans="1:5" ht="80" x14ac:dyDescent="0.2">
+      <c r="A16" s="30" t="s">
+        <v>228</v>
+      </c>
+      <c r="B16" s="30" t="s">
+        <v>229</v>
+      </c>
+      <c r="C16" s="30" t="s">
+        <v>202</v>
+      </c>
+      <c r="D16" s="30" t="s">
         <v>346</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A15" s="33" t="s">
-        <v>226</v>
-      </c>
-      <c r="B15" s="33" t="s">
-        <v>227</v>
-      </c>
-      <c r="C15" s="33" t="s">
-        <v>200</v>
-      </c>
-      <c r="D15" s="33" t="s">
-        <v>228</v>
-      </c>
-      <c r="E15" s="33" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" ht="80" x14ac:dyDescent="0.2">
-      <c r="A16" s="33" t="s">
-        <v>229</v>
-      </c>
-      <c r="B16" s="33" t="s">
+      <c r="E16" s="30" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="32" x14ac:dyDescent="0.2">
+      <c r="A17" s="30" t="s">
         <v>230</v>
       </c>
-      <c r="C16" s="33" t="s">
-        <v>203</v>
-      </c>
-      <c r="D16" s="33" t="s">
-        <v>347</v>
-      </c>
-      <c r="E16" s="33" t="s">
+      <c r="B17" s="30" t="s">
+        <v>231</v>
+      </c>
+      <c r="C17" s="30" t="s">
+        <v>202</v>
+      </c>
+      <c r="D17" s="30" t="s">
+        <v>232</v>
+      </c>
+      <c r="E17" s="30" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="80" x14ac:dyDescent="0.2">
+      <c r="A18" s="30" t="s">
+        <v>233</v>
+      </c>
+      <c r="B18" s="30" t="s">
+        <v>234</v>
+      </c>
+      <c r="C18" s="30" t="s">
+        <v>205</v>
+      </c>
+      <c r="D18" s="30" t="s">
         <v>348</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" ht="32" x14ac:dyDescent="0.2">
-      <c r="A17" s="33" t="s">
-        <v>231</v>
-      </c>
-      <c r="B17" s="33" t="s">
-        <v>232</v>
-      </c>
-      <c r="C17" s="33" t="s">
-        <v>203</v>
-      </c>
-      <c r="D17" s="33" t="s">
-        <v>233</v>
-      </c>
-      <c r="E17" s="33" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" ht="80" x14ac:dyDescent="0.2">
-      <c r="A18" s="33" t="s">
-        <v>234</v>
-      </c>
-      <c r="B18" s="33" t="s">
+      <c r="E18" s="30" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A19" s="30" t="s">
         <v>235</v>
       </c>
-      <c r="C18" s="33" t="s">
-        <v>206</v>
-      </c>
-      <c r="D18" s="33" t="s">
-        <v>349</v>
-      </c>
-      <c r="E18" s="33" t="s">
+      <c r="B19" s="30" t="s">
+        <v>236</v>
+      </c>
+      <c r="C19" s="30" t="s">
+        <v>205</v>
+      </c>
+      <c r="D19" s="30" t="s">
+        <v>237</v>
+      </c>
+      <c r="E19" s="30" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="80" x14ac:dyDescent="0.2">
+      <c r="A20" s="30" t="s">
+        <v>238</v>
+      </c>
+      <c r="B20" s="30" t="s">
+        <v>239</v>
+      </c>
+      <c r="C20" s="30" t="s">
+        <v>199</v>
+      </c>
+      <c r="D20" s="30" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A19" s="33" t="s">
-        <v>236</v>
-      </c>
-      <c r="B19" s="33" t="s">
-        <v>237</v>
-      </c>
-      <c r="C19" s="33" t="s">
-        <v>206</v>
-      </c>
-      <c r="D19" s="33" t="s">
-        <v>238</v>
-      </c>
-      <c r="E19" s="33" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" ht="80" x14ac:dyDescent="0.2">
-      <c r="A20" s="33" t="s">
-        <v>239</v>
-      </c>
-      <c r="B20" s="33" t="s">
+      <c r="E20" s="30" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="32" x14ac:dyDescent="0.2">
+      <c r="A21" s="30" t="s">
         <v>240</v>
       </c>
-      <c r="C20" s="33" t="s">
-        <v>200</v>
-      </c>
-      <c r="D20" s="33" t="s">
-        <v>351</v>
-      </c>
-      <c r="E20" s="33" t="s">
+      <c r="B21" s="30" t="s">
+        <v>241</v>
+      </c>
+      <c r="C21" s="30" t="s">
+        <v>199</v>
+      </c>
+      <c r="D21" s="30" t="s">
+        <v>242</v>
+      </c>
+      <c r="E21" s="30" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="144" x14ac:dyDescent="0.2">
+      <c r="A22" s="30" t="s">
+        <v>243</v>
+      </c>
+      <c r="B22" s="30" t="s">
+        <v>244</v>
+      </c>
+      <c r="C22" s="30" t="s">
+        <v>199</v>
+      </c>
+      <c r="D22" s="30" t="s">
         <v>352</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" ht="32" x14ac:dyDescent="0.2">
-      <c r="A21" s="33" t="s">
-        <v>241</v>
-      </c>
-      <c r="B21" s="33" t="s">
-        <v>242</v>
-      </c>
-      <c r="C21" s="33" t="s">
-        <v>200</v>
-      </c>
-      <c r="D21" s="33" t="s">
-        <v>243</v>
-      </c>
-      <c r="E21" s="33" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" ht="144" x14ac:dyDescent="0.2">
-      <c r="A22" s="33" t="s">
-        <v>244</v>
-      </c>
-      <c r="B22" s="33" t="s">
+      <c r="E22" s="30" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A23" s="30" t="s">
         <v>245</v>
       </c>
-      <c r="C22" s="33" t="s">
-        <v>200</v>
-      </c>
-      <c r="D22" s="33" t="s">
-        <v>353</v>
-      </c>
-      <c r="E22" s="33" t="s">
+      <c r="B23" s="30" t="s">
+        <v>246</v>
+      </c>
+      <c r="C23" s="30" t="s">
+        <v>199</v>
+      </c>
+      <c r="D23" s="30" t="s">
+        <v>247</v>
+      </c>
+      <c r="E23" s="30" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="208" x14ac:dyDescent="0.2">
+      <c r="A24" s="30" t="s">
+        <v>248</v>
+      </c>
+      <c r="B24" s="30" t="s">
+        <v>249</v>
+      </c>
+      <c r="C24" s="30" t="s">
+        <v>202</v>
+      </c>
+      <c r="D24" s="30" t="s">
         <v>354</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A23" s="33" t="s">
-        <v>246</v>
-      </c>
-      <c r="B23" s="33" t="s">
-        <v>247</v>
-      </c>
-      <c r="C23" s="33" t="s">
-        <v>200</v>
-      </c>
-      <c r="D23" s="33" t="s">
-        <v>248</v>
-      </c>
-      <c r="E23" s="33" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" ht="208" x14ac:dyDescent="0.2">
-      <c r="A24" s="33" t="s">
-        <v>249</v>
-      </c>
-      <c r="B24" s="33" t="s">
+      <c r="E24" s="30" t="s">
         <v>250</v>
       </c>
-      <c r="C24" s="33" t="s">
-        <v>203</v>
-      </c>
-      <c r="D24" s="33" t="s">
+    </row>
+    <row r="25" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A25" s="30" t="s">
+        <v>251</v>
+      </c>
+      <c r="B25" s="30" t="s">
+        <v>252</v>
+      </c>
+      <c r="C25" s="30" t="s">
+        <v>202</v>
+      </c>
+      <c r="D25" s="30" t="s">
+        <v>253</v>
+      </c>
+      <c r="E25" s="30" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="112" x14ac:dyDescent="0.2">
+      <c r="A26" s="30" t="s">
+        <v>254</v>
+      </c>
+      <c r="B26" s="30" t="s">
+        <v>255</v>
+      </c>
+      <c r="C26" s="30" t="s">
+        <v>205</v>
+      </c>
+      <c r="D26" s="30" t="s">
         <v>355</v>
       </c>
-      <c r="E24" s="33" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A25" s="33" t="s">
-        <v>252</v>
-      </c>
-      <c r="B25" s="33" t="s">
-        <v>253</v>
-      </c>
-      <c r="C25" s="33" t="s">
-        <v>203</v>
-      </c>
-      <c r="D25" s="33" t="s">
-        <v>254</v>
-      </c>
-      <c r="E25" s="33" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" ht="112" x14ac:dyDescent="0.2">
-      <c r="A26" s="33" t="s">
-        <v>255</v>
-      </c>
-      <c r="B26" s="33" t="s">
+      <c r="E26" s="30" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A27" s="30" t="s">
         <v>256</v>
       </c>
-      <c r="C26" s="33" t="s">
-        <v>206</v>
-      </c>
-      <c r="D26" s="33" t="s">
-        <v>356</v>
-      </c>
-      <c r="E26" s="33" t="s">
+      <c r="B27" s="30" t="s">
+        <v>257</v>
+      </c>
+      <c r="C27" s="30" t="s">
+        <v>205</v>
+      </c>
+      <c r="D27" s="30" t="s">
+        <v>258</v>
+      </c>
+      <c r="E27" s="30" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="112" x14ac:dyDescent="0.2">
+      <c r="A28" s="30" t="s">
+        <v>259</v>
+      </c>
+      <c r="B28" s="30" t="s">
+        <v>260</v>
+      </c>
+      <c r="C28" s="30" t="s">
+        <v>205</v>
+      </c>
+      <c r="D28" s="30" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="27" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A27" s="33" t="s">
-        <v>257</v>
-      </c>
-      <c r="B27" s="33" t="s">
-        <v>258</v>
-      </c>
-      <c r="C27" s="33" t="s">
-        <v>206</v>
-      </c>
-      <c r="D27" s="33" t="s">
-        <v>259</v>
-      </c>
-      <c r="E27" s="33" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" ht="112" x14ac:dyDescent="0.2">
-      <c r="A28" s="33" t="s">
-        <v>260</v>
-      </c>
-      <c r="B28" s="33" t="s">
+      <c r="E28" s="30" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A29" s="30" t="s">
         <v>261</v>
       </c>
-      <c r="C28" s="33" t="s">
-        <v>206</v>
-      </c>
-      <c r="D28" s="33" t="s">
-        <v>358</v>
-      </c>
-      <c r="E28" s="33" t="s">
+      <c r="B29" s="30" t="s">
+        <v>262</v>
+      </c>
+      <c r="C29" s="30" t="s">
+        <v>205</v>
+      </c>
+      <c r="D29" s="30" t="s">
+        <v>263</v>
+      </c>
+      <c r="E29" s="30" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="112" x14ac:dyDescent="0.2">
+      <c r="A30" s="30" t="s">
+        <v>264</v>
+      </c>
+      <c r="B30" s="30" t="s">
+        <v>265</v>
+      </c>
+      <c r="C30" s="30" t="s">
+        <v>205</v>
+      </c>
+      <c r="D30" s="30" t="s">
         <v>359</v>
       </c>
-    </row>
-    <row r="29" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A29" s="33" t="s">
-        <v>262</v>
-      </c>
-      <c r="B29" s="33" t="s">
-        <v>263</v>
-      </c>
-      <c r="C29" s="33" t="s">
-        <v>206</v>
-      </c>
-      <c r="D29" s="33" t="s">
-        <v>264</v>
-      </c>
-      <c r="E29" s="33" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" ht="112" x14ac:dyDescent="0.2">
-      <c r="A30" s="33" t="s">
-        <v>265</v>
-      </c>
-      <c r="B30" s="33" t="s">
+      <c r="E30" s="30" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="32" x14ac:dyDescent="0.2">
+      <c r="A31" s="30" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="33" t="s">
-        <v>206</v>
-      </c>
-      <c r="D30" s="33" t="s">
-        <v>360</v>
-      </c>
-      <c r="E30" s="33" t="s">
+      <c r="B31" s="30" t="s">
+        <v>267</v>
+      </c>
+      <c r="C31" s="30" t="s">
+        <v>205</v>
+      </c>
+      <c r="D31" s="30" t="s">
+        <v>268</v>
+      </c>
+      <c r="E31" s="30" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="48" x14ac:dyDescent="0.2">
+      <c r="A32" s="30" t="s">
+        <v>269</v>
+      </c>
+      <c r="B32" s="30" t="s">
+        <v>270</v>
+      </c>
+      <c r="C32" s="30" t="s">
+        <v>199</v>
+      </c>
+      <c r="D32" s="30" t="s">
         <v>361</v>
       </c>
-    </row>
-    <row r="31" spans="1:5" ht="32" x14ac:dyDescent="0.2">
-      <c r="A31" s="33" t="s">
-        <v>267</v>
-      </c>
-      <c r="B31" s="33" t="s">
-        <v>268</v>
-      </c>
-      <c r="C31" s="33" t="s">
-        <v>206</v>
-      </c>
-      <c r="D31" s="33" t="s">
-        <v>269</v>
-      </c>
-      <c r="E31" s="33" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" ht="48" x14ac:dyDescent="0.2">
-      <c r="A32" s="33" t="s">
-        <v>270</v>
-      </c>
-      <c r="B32" s="33" t="s">
+      <c r="E32" s="30" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="48" x14ac:dyDescent="0.2">
+      <c r="A33" s="30" t="s">
         <v>271</v>
       </c>
-      <c r="C32" s="33" t="s">
-        <v>200</v>
-      </c>
-      <c r="D32" s="33" t="s">
-        <v>362</v>
-      </c>
-      <c r="E32" s="33" t="s">
+      <c r="B33" s="30" t="s">
+        <v>272</v>
+      </c>
+      <c r="C33" s="30" t="s">
+        <v>199</v>
+      </c>
+      <c r="D33" s="30" t="s">
+        <v>273</v>
+      </c>
+      <c r="E33" s="32" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="112" x14ac:dyDescent="0.2">
+      <c r="A34" s="30" t="s">
+        <v>275</v>
+      </c>
+      <c r="B34" s="30" t="s">
+        <v>276</v>
+      </c>
+      <c r="C34" s="30" t="s">
+        <v>199</v>
+      </c>
+      <c r="D34" s="30" t="s">
         <v>363</v>
       </c>
-    </row>
-    <row r="33" spans="1:5" ht="48" x14ac:dyDescent="0.2">
-      <c r="A33" s="33" t="s">
-        <v>272</v>
-      </c>
-      <c r="B33" s="33" t="s">
-        <v>273</v>
-      </c>
-      <c r="C33" s="33" t="s">
-        <v>200</v>
-      </c>
-      <c r="D33" s="33" t="s">
-        <v>274</v>
-      </c>
-      <c r="E33" s="35" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" ht="112" x14ac:dyDescent="0.2">
-      <c r="A34" s="33" t="s">
-        <v>276</v>
-      </c>
-      <c r="B34" s="33" t="s">
+      <c r="E34" s="30" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A35" s="30" t="s">
         <v>277</v>
       </c>
-      <c r="C34" s="33" t="s">
-        <v>200</v>
-      </c>
-      <c r="D34" s="33" t="s">
-        <v>364</v>
-      </c>
-      <c r="E34" s="33" t="s">
+      <c r="B35" s="30" t="s">
+        <v>278</v>
+      </c>
+      <c r="C35" s="30" t="s">
+        <v>199</v>
+      </c>
+      <c r="D35" s="30" t="s">
+        <v>279</v>
+      </c>
+      <c r="E35" s="30" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" ht="160" x14ac:dyDescent="0.2">
+      <c r="A36" s="30" t="s">
+        <v>280</v>
+      </c>
+      <c r="B36" s="30" t="s">
+        <v>281</v>
+      </c>
+      <c r="C36" s="30" t="s">
+        <v>199</v>
+      </c>
+      <c r="D36" s="30" t="s">
         <v>365</v>
       </c>
-    </row>
-    <row r="35" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A35" s="33" t="s">
-        <v>278</v>
-      </c>
-      <c r="B35" s="33" t="s">
-        <v>279</v>
-      </c>
-      <c r="C35" s="33" t="s">
-        <v>200</v>
-      </c>
-      <c r="D35" s="33" t="s">
-        <v>280</v>
-      </c>
-      <c r="E35" s="33" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" ht="160" x14ac:dyDescent="0.2">
-      <c r="A36" s="33" t="s">
-        <v>281</v>
-      </c>
-      <c r="B36" s="33" t="s">
+      <c r="E36" s="30" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="32" x14ac:dyDescent="0.2">
+      <c r="A37" s="30" t="s">
         <v>282</v>
       </c>
-      <c r="C36" s="33" t="s">
-        <v>200</v>
-      </c>
-      <c r="D36" s="33" t="s">
-        <v>366</v>
-      </c>
-      <c r="E36" s="33" t="s">
+      <c r="B37" s="30" t="s">
+        <v>283</v>
+      </c>
+      <c r="C37" s="30" t="s">
+        <v>199</v>
+      </c>
+      <c r="D37" s="30" t="s">
+        <v>284</v>
+      </c>
+      <c r="E37" s="30" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="112" x14ac:dyDescent="0.2">
+      <c r="A38" s="30" t="s">
+        <v>285</v>
+      </c>
+      <c r="B38" s="30" t="s">
+        <v>286</v>
+      </c>
+      <c r="C38" s="30" t="s">
+        <v>205</v>
+      </c>
+      <c r="D38" s="30" t="s">
         <v>367</v>
       </c>
-    </row>
-    <row r="37" spans="1:5" ht="32" x14ac:dyDescent="0.2">
-      <c r="A37" s="33" t="s">
-        <v>283</v>
-      </c>
-      <c r="B37" s="33" t="s">
-        <v>284</v>
-      </c>
-      <c r="C37" s="33" t="s">
-        <v>200</v>
-      </c>
-      <c r="D37" s="33" t="s">
-        <v>285</v>
-      </c>
-      <c r="E37" s="33" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" ht="112" x14ac:dyDescent="0.2">
-      <c r="A38" s="33" t="s">
-        <v>286</v>
-      </c>
-      <c r="B38" s="33" t="s">
+      <c r="E38" s="30" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A39" s="30" t="s">
         <v>287</v>
       </c>
-      <c r="C38" s="33" t="s">
-        <v>206</v>
-      </c>
-      <c r="D38" s="33" t="s">
-        <v>368</v>
-      </c>
-      <c r="E38" s="33" t="s">
+      <c r="B39" s="30" t="s">
+        <v>288</v>
+      </c>
+      <c r="C39" s="30" t="s">
+        <v>205</v>
+      </c>
+      <c r="D39" s="30" t="s">
+        <v>289</v>
+      </c>
+      <c r="E39" s="30" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" ht="80" x14ac:dyDescent="0.2">
+      <c r="A40" s="30" t="s">
+        <v>290</v>
+      </c>
+      <c r="B40" s="30" t="s">
+        <v>291</v>
+      </c>
+      <c r="C40" s="30" t="s">
+        <v>205</v>
+      </c>
+      <c r="D40" s="30" t="s">
         <v>369</v>
       </c>
-    </row>
-    <row r="39" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A39" s="33" t="s">
-        <v>288</v>
-      </c>
-      <c r="B39" s="33" t="s">
-        <v>289</v>
-      </c>
-      <c r="C39" s="33" t="s">
-        <v>206</v>
-      </c>
-      <c r="D39" s="33" t="s">
-        <v>290</v>
-      </c>
-      <c r="E39" s="33" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" ht="80" x14ac:dyDescent="0.2">
-      <c r="A40" s="33" t="s">
-        <v>291</v>
-      </c>
-      <c r="B40" s="33" t="s">
+      <c r="E40" s="30" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" ht="32" x14ac:dyDescent="0.2">
+      <c r="A41" s="30" t="s">
         <v>292</v>
       </c>
-      <c r="C40" s="33" t="s">
-        <v>206</v>
-      </c>
-      <c r="D40" s="33" t="s">
-        <v>370</v>
-      </c>
-      <c r="E40" s="33" t="s">
+      <c r="B41" s="30" t="s">
+        <v>293</v>
+      </c>
+      <c r="C41" s="30" t="s">
+        <v>205</v>
+      </c>
+      <c r="D41" s="30" t="s">
+        <v>294</v>
+      </c>
+      <c r="E41" s="30" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" ht="64" x14ac:dyDescent="0.2">
+      <c r="A42" s="30" t="s">
+        <v>295</v>
+      </c>
+      <c r="B42" s="30" t="s">
+        <v>296</v>
+      </c>
+      <c r="C42" s="30" t="s">
+        <v>199</v>
+      </c>
+      <c r="D42" s="30" t="s">
         <v>371</v>
       </c>
-    </row>
-    <row r="41" spans="1:5" ht="32" x14ac:dyDescent="0.2">
-      <c r="A41" s="33" t="s">
-        <v>293</v>
-      </c>
-      <c r="B41" s="33" t="s">
-        <v>294</v>
-      </c>
-      <c r="C41" s="33" t="s">
-        <v>206</v>
-      </c>
-      <c r="D41" s="33" t="s">
-        <v>295</v>
-      </c>
-      <c r="E41" s="33" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" ht="64" x14ac:dyDescent="0.2">
-      <c r="A42" s="33" t="s">
-        <v>296</v>
-      </c>
-      <c r="B42" s="33" t="s">
+      <c r="E42" s="30" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A43" s="30" t="s">
         <v>297</v>
       </c>
-      <c r="C42" s="33" t="s">
-        <v>200</v>
-      </c>
-      <c r="D42" s="33" t="s">
-        <v>372</v>
-      </c>
-      <c r="E42" s="33" t="s">
+      <c r="B43" s="30" t="s">
+        <v>298</v>
+      </c>
+      <c r="C43" s="30" t="s">
+        <v>199</v>
+      </c>
+      <c r="D43" s="30" t="s">
+        <v>299</v>
+      </c>
+      <c r="E43" s="30" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" ht="48" x14ac:dyDescent="0.2">
+      <c r="A44" s="30" t="s">
+        <v>300</v>
+      </c>
+      <c r="B44" s="30" t="s">
+        <v>301</v>
+      </c>
+      <c r="C44" s="30" t="s">
+        <v>199</v>
+      </c>
+      <c r="D44" s="30" t="s">
         <v>373</v>
       </c>
-    </row>
-    <row r="43" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A43" s="33" t="s">
-        <v>298</v>
-      </c>
-      <c r="B43" s="33" t="s">
-        <v>299</v>
-      </c>
-      <c r="C43" s="33" t="s">
-        <v>200</v>
-      </c>
-      <c r="D43" s="33" t="s">
-        <v>300</v>
-      </c>
-      <c r="E43" s="33" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" ht="48" x14ac:dyDescent="0.2">
-      <c r="A44" s="33" t="s">
-        <v>301</v>
-      </c>
-      <c r="B44" s="33" t="s">
+      <c r="E44" s="30" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" ht="32" x14ac:dyDescent="0.2">
+      <c r="A45" s="30" t="s">
         <v>302</v>
       </c>
-      <c r="C44" s="33" t="s">
-        <v>200</v>
-      </c>
-      <c r="D44" s="33" t="s">
-        <v>374</v>
-      </c>
-      <c r="E44" s="33" t="s">
+      <c r="B45" s="30" t="s">
+        <v>303</v>
+      </c>
+      <c r="C45" s="30" t="s">
+        <v>199</v>
+      </c>
+      <c r="D45" s="30" t="s">
+        <v>304</v>
+      </c>
+      <c r="E45" s="30" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" ht="112" x14ac:dyDescent="0.2">
+      <c r="A46" s="30" t="s">
+        <v>305</v>
+      </c>
+      <c r="B46" s="30" t="s">
+        <v>306</v>
+      </c>
+      <c r="C46" s="30" t="s">
+        <v>205</v>
+      </c>
+      <c r="D46" s="30" t="s">
+        <v>329</v>
+      </c>
+      <c r="E46" s="30" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" ht="48" x14ac:dyDescent="0.2">
+      <c r="A47" s="30" t="s">
+        <v>307</v>
+      </c>
+      <c r="B47" s="30" t="s">
+        <v>308</v>
+      </c>
+      <c r="C47" s="30" t="s">
+        <v>205</v>
+      </c>
+      <c r="D47" s="30" t="s">
+        <v>331</v>
+      </c>
+      <c r="E47" s="30" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A48" s="31" t="s">
+        <v>309</v>
+      </c>
+      <c r="B48" s="31"/>
+      <c r="C48" s="31"/>
+      <c r="D48" s="31"/>
+      <c r="E48" s="31"/>
+    </row>
+    <row r="49" spans="1:5" ht="32" x14ac:dyDescent="0.2">
+      <c r="A49" s="30" t="s">
+        <v>310</v>
+      </c>
+      <c r="B49" s="30" t="s">
+        <v>311</v>
+      </c>
+      <c r="C49" s="30" t="s">
+        <v>199</v>
+      </c>
+      <c r="D49" s="30" t="s">
         <v>375</v>
       </c>
-    </row>
-    <row r="45" spans="1:5" ht="32" x14ac:dyDescent="0.2">
-      <c r="A45" s="33" t="s">
-        <v>303</v>
-      </c>
-      <c r="B45" s="33" t="s">
-        <v>304</v>
-      </c>
-      <c r="C45" s="33" t="s">
-        <v>200</v>
-      </c>
-      <c r="D45" s="33" t="s">
+      <c r="E49" s="30" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" ht="32" x14ac:dyDescent="0.2">
+      <c r="A50" s="30" t="s">
+        <v>312</v>
+      </c>
+      <c r="B50" s="30" t="s">
+        <v>313</v>
+      </c>
+      <c r="C50" s="30" t="s">
+        <v>199</v>
+      </c>
+      <c r="D50" s="30" t="s">
+        <v>314</v>
+      </c>
+      <c r="E50" s="30" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" ht="32" x14ac:dyDescent="0.2">
+      <c r="A51" s="30" t="s">
+        <v>316</v>
+      </c>
+      <c r="B51" s="30" t="s">
+        <v>317</v>
+      </c>
+      <c r="C51" s="30" t="s">
+        <v>199</v>
+      </c>
+      <c r="D51" s="30" t="s">
+        <v>377</v>
+      </c>
+      <c r="E51" s="30" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A52" s="30" t="s">
+        <v>318</v>
+      </c>
+      <c r="B52" s="30" t="s">
+        <v>319</v>
+      </c>
+      <c r="C52" s="30" t="s">
+        <v>199</v>
+      </c>
+      <c r="D52" s="30" t="s">
+        <v>320</v>
+      </c>
+      <c r="E52" s="30" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" ht="32" x14ac:dyDescent="0.2">
+      <c r="A53" s="30" t="s">
+        <v>322</v>
+      </c>
+      <c r="B53" s="30" t="s">
+        <v>323</v>
+      </c>
+      <c r="C53" s="30" t="s">
+        <v>199</v>
+      </c>
+      <c r="D53" s="30" t="s">
+        <v>379</v>
+      </c>
+      <c r="E53" s="30" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" ht="32" x14ac:dyDescent="0.2">
+      <c r="A54" s="33" t="s">
+        <v>324</v>
+      </c>
+      <c r="B54" s="33" t="s">
+        <v>325</v>
+      </c>
+      <c r="C54" s="33" t="s">
+        <v>199</v>
+      </c>
+      <c r="D54" s="33" t="s">
+        <v>326</v>
+      </c>
+      <c r="E54" s="33" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="36" t="s">
+        <v>332</v>
+      </c>
+      <c r="B56" s="37"/>
+      <c r="C56" s="37"/>
+      <c r="D56" s="37"/>
+      <c r="E56" s="38"/>
+    </row>
+    <row r="57" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="20" t="s">
+        <v>333</v>
+      </c>
+      <c r="B57" s="34" t="s">
+        <v>334</v>
+      </c>
+      <c r="C57" s="34"/>
+      <c r="D57" s="34"/>
+      <c r="E57" s="34"/>
+    </row>
+    <row r="58" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="20" t="s">
+        <v>335</v>
+      </c>
+      <c r="B58" s="34" t="s">
         <v>305</v>
       </c>
-      <c r="E45" s="33" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" ht="112" x14ac:dyDescent="0.2">
-      <c r="A46" s="33" t="s">
-        <v>306</v>
-      </c>
-      <c r="B46" s="33" t="s">
-        <v>307</v>
-      </c>
-      <c r="C46" s="33" t="s">
-        <v>206</v>
-      </c>
-      <c r="D46" s="33" t="s">
-        <v>330</v>
-      </c>
-      <c r="E46" s="33" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" ht="48" x14ac:dyDescent="0.2">
-      <c r="A47" s="33" t="s">
-        <v>308</v>
-      </c>
-      <c r="B47" s="33" t="s">
-        <v>309</v>
-      </c>
-      <c r="C47" s="33" t="s">
-        <v>206</v>
-      </c>
-      <c r="D47" s="33" t="s">
-        <v>332</v>
-      </c>
-      <c r="E47" s="33" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A48" s="36" t="s">
-        <v>310</v>
-      </c>
-      <c r="B48" s="36"/>
-      <c r="C48" s="36"/>
-      <c r="D48" s="36"/>
-      <c r="E48" s="36"/>
-    </row>
-    <row r="49" spans="1:5" ht="32" x14ac:dyDescent="0.2">
-      <c r="A49" s="33" t="s">
-        <v>311</v>
-      </c>
-      <c r="B49" s="33" t="s">
-        <v>312</v>
-      </c>
-      <c r="C49" s="33" t="s">
-        <v>200</v>
-      </c>
-      <c r="D49" s="33" t="s">
-        <v>376</v>
-      </c>
-      <c r="E49" s="33" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" ht="32" x14ac:dyDescent="0.2">
-      <c r="A50" s="33" t="s">
-        <v>313</v>
-      </c>
-      <c r="B50" s="33" t="s">
-        <v>314</v>
-      </c>
-      <c r="C50" s="33" t="s">
-        <v>200</v>
-      </c>
-      <c r="D50" s="33" t="s">
-        <v>315</v>
-      </c>
-      <c r="E50" s="33" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" ht="32" x14ac:dyDescent="0.2">
-      <c r="A51" s="33" t="s">
-        <v>317</v>
-      </c>
-      <c r="B51" s="33" t="s">
-        <v>318</v>
-      </c>
-      <c r="C51" s="33" t="s">
-        <v>200</v>
-      </c>
-      <c r="D51" s="33" t="s">
-        <v>378</v>
-      </c>
-      <c r="E51" s="33" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A52" s="33" t="s">
-        <v>319</v>
-      </c>
-      <c r="B52" s="33" t="s">
-        <v>320</v>
-      </c>
-      <c r="C52" s="33" t="s">
-        <v>200</v>
-      </c>
-      <c r="D52" s="33" t="s">
-        <v>321</v>
-      </c>
-      <c r="E52" s="33" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" ht="32" x14ac:dyDescent="0.2">
-      <c r="A53" s="33" t="s">
-        <v>323</v>
-      </c>
-      <c r="B53" s="33" t="s">
-        <v>324</v>
-      </c>
-      <c r="C53" s="33" t="s">
-        <v>200</v>
-      </c>
-      <c r="D53" s="33" t="s">
-        <v>380</v>
-      </c>
-      <c r="E53" s="33" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" ht="32" x14ac:dyDescent="0.2">
-      <c r="A54" s="37" t="s">
-        <v>325</v>
-      </c>
-      <c r="B54" s="37" t="s">
-        <v>326</v>
-      </c>
-      <c r="C54" s="37" t="s">
-        <v>200</v>
-      </c>
-      <c r="D54" s="37" t="s">
-        <v>327</v>
-      </c>
-      <c r="E54" s="37" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="20" t="s">
-        <v>333</v>
-      </c>
-      <c r="B56" s="21"/>
-      <c r="C56" s="21"/>
-      <c r="D56" s="21"/>
-      <c r="E56" s="22"/>
-    </row>
-    <row r="57" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="23" t="s">
-        <v>334</v>
-      </c>
-      <c r="B57" s="38" t="s">
-        <v>335</v>
-      </c>
-      <c r="C57" s="38"/>
-      <c r="D57" s="38"/>
-      <c r="E57" s="38"/>
-    </row>
-    <row r="58" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="23" t="s">
+      <c r="C58" s="34"/>
+      <c r="D58" s="34"/>
+      <c r="E58" s="34"/>
+    </row>
+    <row r="59" spans="1:5" ht="61.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="20" t="s">
         <v>336</v>
       </c>
-      <c r="B58" s="38" t="s">
-        <v>306</v>
-      </c>
-      <c r="C58" s="38"/>
-      <c r="D58" s="38"/>
-      <c r="E58" s="38"/>
-    </row>
-    <row r="59" spans="1:5" ht="61.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="23" t="s">
+      <c r="B59" s="34" t="s">
         <v>337</v>
       </c>
-      <c r="B59" s="38" t="s">
+      <c r="C59" s="34"/>
+      <c r="D59" s="34"/>
+      <c r="E59" s="34"/>
+    </row>
+    <row r="60" spans="1:5" ht="61.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A60" s="20" t="s">
         <v>338</v>
       </c>
-      <c r="C59" s="38"/>
-      <c r="D59" s="38"/>
-      <c r="E59" s="38"/>
-    </row>
-    <row r="60" spans="1:5" ht="61.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="23" t="s">
+      <c r="B60" s="34" t="s">
         <v>339</v>
       </c>
-      <c r="B60" s="38" t="s">
+      <c r="C60" s="34"/>
+      <c r="D60" s="34"/>
+      <c r="E60" s="34"/>
+    </row>
+    <row r="61" spans="1:5" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="20" t="s">
         <v>340</v>
       </c>
-      <c r="C60" s="38"/>
-      <c r="D60" s="38"/>
-      <c r="E60" s="38"/>
-    </row>
-    <row r="61" spans="1:5" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="23" t="s">
+      <c r="B61" s="34" t="s">
         <v>341</v>
       </c>
-      <c r="B61" s="38" t="s">
-        <v>342</v>
-      </c>
-      <c r="C61" s="38"/>
-      <c r="D61" s="38"/>
-      <c r="E61" s="38"/>
+      <c r="C61" s="34"/>
+      <c r="D61" s="34"/>
+      <c r="E61" s="34"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -7129,57 +7227,57 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>195</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
+        <v>196</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" t="s">
         <v>198</v>
-      </c>
-      <c r="C2" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
+        <v>199</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="C3" t="s">
         <v>201</v>
-      </c>
-      <c r="C3" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
+        <v>202</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="C4" t="s">
         <v>204</v>
-      </c>
-      <c r="C4" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
+        <v>205</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>206</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="C5" t="s">
         <v>207</v>
-      </c>
-      <c r="C5" t="s">
-        <v>208</v>
       </c>
     </row>
   </sheetData>
